--- a/artfynd/A 14915-2025 artfynd.xlsx
+++ b/artfynd/A 14915-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127919571</v>
       </c>
       <c r="B2" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14915-2025 artfynd.xlsx
+++ b/artfynd/A 14915-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127919571</v>
       </c>
       <c r="B2" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14915-2025 artfynd.xlsx
+++ b/artfynd/A 14915-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127919571</v>
       </c>
       <c r="B2" t="n">
-        <v>56615</v>
+        <v>56618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14915-2025 artfynd.xlsx
+++ b/artfynd/A 14915-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127919571</v>
       </c>
       <c r="B2" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
